--- a/pensum/ma05/MA05_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma05/MA05_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="154">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Markedsføring kapittel 5: Markedssegmentering (V5)</t>
   </si>
@@ -173,9 +173,18 @@
     <t xml:space="preserve">a)  Hvor stor var omsetningen i segmentet borettslag? Andelen ganger hele omsetningen.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formel og begrep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segmentets omsetning = andel × total omsetning. Første krav til en målgruppe er at segmentet kan identifiseres, beskrives og måles (Markedsføring 5.7).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Huseiere og næringsbygg står for 20 % av omsetningen hver. Hvor mange flere montørtimer bruker huseierne enn næringsbyggene?</t>
   </si>
   <si>
+    <t xml:space="preserve">Segmentets timer = andel × totale timer. Det største segmentet er ikke alltid det mest lønnsomme (Markedsføring 5.7).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Nordlys skiller mellom entreprenører, næringsbygg og offentlige rammeavtaler. Hvilket av bokas fire kriterier på bedriftsmarkedet er det først og fremst?   A: Beliggenhet   B: Bransje   C: Viktighet for bedriften   (skriv bokstaven)</t>
   </si>
   <si>
@@ -185,6 +194,24 @@
     <t xml:space="preserve">e)  Nordlys gir i dag alle fem kundetypene samme tilbud. Velg ett segment, og forklar hva det trenger annerledes enn de andre, og hva både kunden og Nordlys vinner på et tilbud som er laget for det. To–tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Segmentering ivaretar begge parter: kunden får større behovstilfredsstillelse, og selgeren større konkurransedyktighet (Markedsføring 5.2). Differensieringen kan knyttes til produkt, pris, distribusjon, kommunikasjon eller service (5.8.2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hint, hvis du står fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fra andel til kroner og timer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Omsetning i et segment = andelen × 22 400 000. Timer i et segment = andelen × 14 400. Regn begge for huseiere og næringsbygg, og trekk fra.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kriteriet og Karis påstand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bokas fire kriterier på bedriftsmarkedet er størrelse, bransje, beliggenhet og viktighet (5.6). Se på kolonnen for timer: får Nordlys like mye igjen for timene som for omsetningen?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 5, avsnitt 5.1–5.2 (segmentering) og 5.6 (segmenteringskriterier på bedriftsmarkedet). Andelene er de samme som i appen og sammendraget til kapittel 5. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -275,12 +302,30 @@
     <t xml:space="preserve">c)  Hvor mange sikringsskapbytter i året gir segmentet «eneboliger bygd før 1980», med Monas antagelse om 5 %?</t>
   </si>
   <si>
+    <t xml:space="preserve">Segmentets størrelse = antall × andel × andel. Segmenter kan identifiseres og måles med offentlig statistikk supplert med rimelige antagelser (Markedsføring 5.7).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Mona vil bruke «miljøbevisste huseiere» som eneste kriterium for å finne solcellekunder. Hva er problemet, ifølge boka?   A: Psykografiske kriterier er ikke tillatt å bruke i Norge   B: Livsstil er vanskelig å fastslå: Fjell kan verken telle eller finne disse kundene uten et demografisk kriterium i tillegg   C: Livsstil er et kriterium for bedriftsmarkedet, ikke for boliger   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Hvilket boligsegment bør Mona beskrive først, og med hvilke to kriterier? Bruk tallene du har regnet, og si om segmentet passer Fjells kapasitet. To–tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Demografiske kriterier (Markedsføring 5.4), identifiserbarhet og tilpasning til kapasitet (5.7).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brukbart eller ikke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spør for hvert kriterium: vil gruppene ha forskjellige ting av en elektriker? Lett å måle er ikke nok (5.4).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segmentets størrelse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antall eneboliger × andelen bygd før 1980 × andelen som bytter skap i året. Gang med 6 timer og sammenlikn med 3 500.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 5, avsnitt 5.4 (demografiske kriterier), 5.5 (psykografiske kriterier) og 5.7 (identifiserbarhet med offentlig statistikk og rimelige antagelser). Sikringsskapbyttet på 6 timer er fra OK07. Fjell Elektro AS og Haugerud Bygg AS er konstruerte casebedrifter; boligtallene for Oslo øst er konstruerte.</t>
   </si>
   <si>
@@ -323,9 +368,15 @@
     <t xml:space="preserve">a)  Hvor mye gir borettslagene i dekningsbidrag per montørtime? Omsetning ganger bruttofortjeneste i prosent, delt på timene, minus 640 kr i direkte lønn per time. Svar i hele kroner.</t>
   </si>
   <si>
+    <t xml:space="preserve">Dekningsbidrag per montørtime = omsetning × bruttofortjeneste i % / timer − direkte lønn per time. Dekningsbidrag = salgsinntekt − variable kostnader (Økonomistyring kap. 2); knapp faktor (kap. 7). Ikke fra Markedsføring kap. 5.</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Nordlys flytter 500 montørtimer i året fra entreprenører (179 kr i dekningsbidrag per time) til service på næringsbygg (916 kr per time). Hvor mye øker dekningsbidraget?</t>
   </si>
   <si>
+    <t xml:space="preserve">Endring i dekningsbidrag = timer flyttet × (DB per time i nytt segment − DB per time i gammelt). Knapp faktor (Økonomistyring kap. 7).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Nordlys lager en serviceavtale med to timers responstid for næringsbygg og et eget tilbudsoppsett for borettslagsstyrer, og tar huseiere når de ringer. Hvilken målgruppestrategi er det?   A: Udifferensiert markedsføring   B: Differensiert markedsføring   C: Konsentrert markedsføring   (skriv bokstaven)</t>
   </si>
   <si>
@@ -335,6 +386,21 @@
     <t xml:space="preserve">e)  Anbefal Kari to målgrupper og en målgruppestrategi. Test valget mot de fire kravene i boka, og si hva Nordlys gjør med de andre segmentene. Bruk minst ett tall. Tre–fire setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Valg av målgrupper og de fire kravene (Markedsføring 5.7), målgruppestrategier (5.8), dekningsbidrag per knapp faktor (Økonomistyring kap. 7).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kroner per time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bruttofortjeneste = omsetning × prosenten. Del på segmentets timer, og trekk fra 640 kr i lønn: da har du dekningsbidrag per montørtime. Gevinsten ved å flytte timer = timer × (ny kr per time − gammel kr per time).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategi og prosenten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samme tilbud til alle, ulike tilbud til ulike grupper, eller alt på ett segment (5.8). Prosenten i tabellen er per omsetningskrone; hva er knapt hos Nordlys?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 5, avsnitt 5.7 (valg av målgrupper, fire krav, lønnsomhetspotensial) og 5.8 (målgruppestrategier). Dekningsbidrag per montørtime: Hjertnes og Skorpen, Økonomistyring for LØM-emnet, kap. 2 (dekningsbidrag = salgsinntekt − variable kostnader) og kap. 7 (knapp faktor). Direkte lønn 640 kr per montørtime som i oppdragskalkylene (Økonomistyring kap. 5). Tallene er de samme som i appen og sammendraget til kapittel 5. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -386,9 +452,15 @@
     <t xml:space="preserve">a)  Hvor mange fakturerbare timer har Fjell Elektro på et halvår, med 3 500 timer i året jevnt fordelt?</t>
   </si>
   <si>
+    <t xml:space="preserve">Kapasitet i en periode = årskapasitet × periodens andel av året. Ingen formel i Markedsføring kap. 5; tallet er grunnlaget for kravet om tilpasning til kapasitet (5.7).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hvor stor andel av Fjells timer i det halvåret krever Haugerud-prosjektet? Svar i prosent med én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Andel i prosent = del / helhet × 100. Bedriften må kunne levere de mengdene som etterspørres til rett tidspunkt (Markedsføring 5.7).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Hvilket av lærebokas fire krav til en målgruppe er det tydeligst at entreprenørsegmentet ikke oppfyller for Fjell i dag?   A: Identifiserbart og målbart   B: Stort nok   C: Tilpasset bedriftens kapasitet og ressurser   (skriv bokstaven)</t>
   </si>
   <si>
@@ -396,6 +468,21 @@
   </si>
   <si>
     <t xml:space="preserve">e)  Bør Fjell Elektro ta Haugerud-prosjektet og satse på entreprenørmarkedet? Gi Mona en anbefaling med minst ett tall og én risiko. Tre setninger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tilpasning til kapasitet (Markedsføring 5.7), konsentrert og differensiert markedsføring (5.8.2–5.8.3). Kredittid og likviditet er fra Økonomistyring kap. 9.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kapasiteten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timer på et halvår = 3 500 / 2. Prosjektets andel = 1 800 delt på halvårets timer × 100. Over 100 % betyr at ingen andre kunder får timer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riktig ord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boka bruker «differensiert» om ulike tilbud til ulike grupper (5.8.2) og «konsentrert» om å satse på ett eller noen få segmenter (5.8.3).</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 5.7 (fire krav, kapasitet) og 5.8 (målgruppestrategier); kap. 3.7.2 (Porter). Haugerud-prosjektet er fra MA02; konkurser i bygg: BDO gjengitt i Elektro24-7. Fjell Elektro AS og Haugerud Bygg AS er konstruerte casebedrifter; boligtallene for Oslo øst er konstruerte.</t>
@@ -409,7 +496,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\−#,##0.##;\0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -476,8 +563,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F4A6D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -493,13 +602,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F6FA"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEEF2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFF4F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8954A"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF6EA"/>
+        <bgColor rgb="FFF4F6FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -552,7 +679,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -629,11 +756,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -682,8 +829,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF4F6FA"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFBF6EA"/>
+      <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -697,7 +844,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF4F6FA"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -711,7 +858,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5E6670"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB8954A"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -1014,7 +1161,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1172,35 +1319,20 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="18" t="str">
-        <f aca="false">IF(F18="","",IF(ABS(F18-(1728))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+      <c r="B18" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="18" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+    </row>
+    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
         <v>51</v>
       </c>
@@ -1208,84 +1340,181 @@
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="19"/>
+      <c r="F20" s="17"/>
       <c r="G20" s="18" t="str">
-        <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F20="","",IF(ABS(F20-(1728))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="20"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="20"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-    </row>
-    <row r="26" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+    </row>
+    <row r="23" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="18" t="str">
+        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="18" t="str">
+        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+    </row>
+    <row r="29" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+    </row>
+    <row r="36" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="B18:G18"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:G24"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:G28"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1302,7 +1531,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1313,7 +1542,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1323,7 +1552,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1334,7 +1563,7 @@
     </row>
     <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1345,10 +1574,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -1357,11 +1586,11 @@
       <c r="G7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
-        <v>60</v>
+      <c r="A8" s="26" t="s">
+        <v>69</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1370,11 +1599,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
-        <v>62</v>
+      <c r="A9" s="26" t="s">
+        <v>71</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1383,11 +1612,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
-        <v>64</v>
+      <c r="A10" s="26" t="s">
+        <v>73</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1396,11 +1625,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
-        <v>66</v>
+      <c r="A11" s="26" t="s">
+        <v>75</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1409,11 +1638,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
-        <v>68</v>
+      <c r="A12" s="26" t="s">
+        <v>77</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1422,11 +1651,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
-        <v>70</v>
+      <c r="A13" s="26" t="s">
+        <v>79</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1435,11 +1664,11 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
-        <v>72</v>
+      <c r="A14" s="26" t="s">
+        <v>81</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1464,13 +1693,13 @@
     </row>
     <row r="17" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="19"/>
+      <c r="F17" s="21"/>
       <c r="G17" s="18" t="str">
         <f aca="false">IF(F17="","",IF(UPPER(TRIM(F17))="A","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1478,7 +1707,7 @@
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1487,13 +1716,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="19"/>
+      <c r="F19" s="21"/>
       <c r="G19" s="18" t="str">
         <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1501,13 +1730,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="19"/>
+      <c r="F20" s="21"/>
       <c r="G20" s="18" t="str">
         <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1515,13 +1744,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="19"/>
+      <c r="F21" s="21"/>
       <c r="G21" s="18" t="str">
         <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1529,13 +1758,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="19"/>
+      <c r="F22" s="21"/>
       <c r="G22" s="18" t="str">
         <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1543,13 +1772,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="19"/>
+      <c r="F23" s="21"/>
       <c r="G23" s="18" t="str">
         <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1557,13 +1786,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="19"/>
+      <c r="F24" s="21"/>
       <c r="G24" s="18" t="str">
         <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1571,7 +1800,7 @@
     </row>
     <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -1583,80 +1812,143 @@
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="18" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="B","Riktig","Prøv igjen"))</f>
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+    </row>
+    <row r="28" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="18" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="B","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="20"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="20"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
+    <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="20"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-    </row>
-    <row r="32" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+    </row>
+    <row r="40" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="30">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1677,11 +1969,16 @@
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A28:G30"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A41:G41"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1698,7 +1995,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1709,7 +2006,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1719,7 +2016,7 @@
     </row>
     <row r="4" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1730,7 +2027,7 @@
     </row>
     <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1744,26 +2041,26 @@
         <v>24</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="27" t="n">
         <v>4480000</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" s="22" t="n">
+        <v>107</v>
+      </c>
+      <c r="D8" s="27" t="n">
         <v>3600</v>
       </c>
     </row>
@@ -1771,13 +2068,13 @@
       <c r="A9" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="23" t="n">
+      <c r="B9" s="28" t="n">
         <v>3136000</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" s="23" t="n">
+        <v>108</v>
+      </c>
+      <c r="D9" s="28" t="n">
         <v>2160</v>
       </c>
     </row>
@@ -1785,13 +2082,13 @@
       <c r="A10" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="22" t="n">
+      <c r="B10" s="27" t="n">
         <v>7616000</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D10" s="22" t="n">
+        <v>109</v>
+      </c>
+      <c r="D10" s="27" t="n">
         <v>5184</v>
       </c>
     </row>
@@ -1799,27 +2096,27 @@
       <c r="A11" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="23" t="n">
+      <c r="B11" s="28" t="n">
         <v>4480000</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D11" s="23" t="n">
+        <v>108</v>
+      </c>
+      <c r="D11" s="28" t="n">
         <v>1872</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="B12" s="22" t="n">
+        <v>110</v>
+      </c>
+      <c r="B12" s="27" t="n">
         <v>2688000</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12" s="22" t="n">
+        <v>111</v>
+      </c>
+      <c r="D12" s="27" t="n">
         <v>1584</v>
       </c>
     </row>
@@ -1827,13 +2124,13 @@
       <c r="A13" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="29" t="n">
         <v>22400000</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" s="24" t="n">
+        <v>112</v>
+      </c>
+      <c r="D13" s="29" t="n">
         <v>14400</v>
       </c>
     </row>
@@ -1865,7 +2162,7 @@
     </row>
     <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -1877,120 +2174,202 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="18" t="str">
-        <f aca="false">IF(F18="","",IF(ABS(F18-(368500))&lt;=500,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="18" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+    </row>
+    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="19"/>
+      <c r="F20" s="17"/>
       <c r="G20" s="18" t="str">
-        <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F20="","",IF(ABS(F20-(368500))&lt;=500,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="20"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="20"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-    </row>
-    <row r="26" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+    </row>
+    <row r="23" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="18" t="str">
+        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="18" t="str">
+        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+    </row>
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+    </row>
+    <row r="33" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+    </row>
+    <row r="36" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="B18:G18"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:G24"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:G28"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2007,7 +2386,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -2018,7 +2397,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2028,7 +2407,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2039,7 +2418,7 @@
     </row>
     <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2050,10 +2429,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -2062,11 +2441,11 @@
       <c r="G7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
-        <v>70</v>
+      <c r="A8" s="26" t="s">
+        <v>79</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -2075,11 +2454,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
-        <v>107</v>
+      <c r="A9" s="26" t="s">
+        <v>129</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -2088,11 +2467,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
-        <v>109</v>
+      <c r="A10" s="26" t="s">
+        <v>131</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -2101,11 +2480,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
-        <v>111</v>
+      <c r="A11" s="26" t="s">
+        <v>133</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2114,11 +2493,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
-        <v>113</v>
+      <c r="A12" s="26" t="s">
+        <v>135</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -2127,11 +2506,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
-        <v>115</v>
+      <c r="A13" s="26" t="s">
+        <v>137</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -2140,11 +2519,11 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
-        <v>117</v>
+      <c r="A14" s="26" t="s">
+        <v>139</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -2169,7 +2548,7 @@
     </row>
     <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -2181,108 +2560,184 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="18" t="str">
-        <f aca="false">IF(F18="","",IF(ABS(F18-(102.9))&lt;=0.1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="18" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="C","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+    </row>
+    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="19"/>
+      <c r="F20" s="17"/>
       <c r="G20" s="18" t="str">
-        <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F20="","",IF(ABS(F20-(102.9))&lt;=0.1,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="20"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="20"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-    </row>
-    <row r="26" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+    </row>
+    <row r="23" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="18" t="str">
+        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="C","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="18" t="str">
+        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+    </row>
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+    </row>
+    <row r="36" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="25">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2295,13 +2750,19 @@
     <mergeCell ref="B14:G14"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="B18:G18"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:G24"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:G28"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/pensum/ma05/MA05_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma05/MA05_Klasseoppgaver_v5.xlsx
@@ -326,7 +326,7 @@
     <t xml:space="preserve">Antall eneboliger × andelen bygd før 1980 × andelen som bytter skap i året. Gang med 6 timer og sammenlikn med 3 500.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 5, avsnitt 5.4 (demografiske kriterier), 5.5 (psykografiske kriterier) og 5.7 (identifiserbarhet med offentlig statistikk og rimelige antagelser). Sikringsskapbyttet på 6 timer er fra OK07. Fjell Elektro AS og Haugerud Bygg AS er konstruerte casebedrifter; boligtallene for Oslo øst er konstruerte.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 5, avsnitt 5.4 (demografiske kriterier), 5.5 (psykografiske kriterier) og 5.7 (identifiserbarhet med offentlig statistikk og rimelige antagelser). Sikringsskapbyttet på 6 timer er fra Økonomistyring kap. 7. Fjell Elektro AS og Haugerud Bygg AS er konstruerte casebedrifter; boligtallene for Oslo øst er konstruerte.</t>
   </si>
   <si>
     <t xml:space="preserve">B1 · Nordlys: hvilke segmenter skal bli målgrupper?</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">Omsetning, kr</t>
   </si>
   <si>
-    <t xml:space="preserve">Bruttofortj. %</t>
+    <t xml:space="preserve">Brutto­fortjeneste, %</t>
   </si>
   <si>
     <t xml:space="preserve">Timer</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">b)  Nordlys flytter 500 montørtimer i året fra entreprenører (179 kr i dekningsbidrag per time) til service på næringsbygg (916 kr per time). Hvor mye øker dekningsbidraget?</t>
   </si>
   <si>
-    <t xml:space="preserve">Endring i dekningsbidrag = timer flyttet × (DB per time i nytt segment − DB per time i gammelt). Knapp faktor (Økonomistyring kap. 7).</t>
+    <t xml:space="preserve">Endring i dekningsbidrag = timer flyttet × (dekningsbidrag per time i nytt segment − dekningsbidrag per time i gammelt). Knapp faktor (Økonomistyring kap. 7).</t>
   </si>
   <si>
     <t xml:space="preserve">c)  Nordlys lager en serviceavtale med to timers responstid for næringsbygg og et eget tilbudsoppsett for borettslagsstyrer, og tar huseiere når de ringer. Hvilken målgruppestrategi er det?   A: Udifferensiert markedsføring   B: Differensiert markedsføring   C: Konsentrert markedsføring   (skriv bokstaven)</t>
   </si>
   <si>
-    <t xml:space="preserve">d)  Huseierne har Nordlys' høyeste bruttofortjeneste i prosent av omsetningen, 75,0 %. Ronny sier at de derfor er det mest lønnsomme segmentet. Hva er riktig?   A: Ja: høyest prosent av omsetningen betyr mest lønnsomt   B: Nei: prosenten er av omsetningen. Når timen er knapp, gir huseierne 293 kr i DB per time mot næringsbyggenes 916   C: Nei: huseierne betaler for sent til å være lønnsomme   (skriv bokstaven)</t>
+    <t xml:space="preserve">d)  Huseierne har Nordlys' høyeste bruttofortjeneste i prosent av omsetningen, 75,0 %. Ronny sier at de derfor er det mest lønnsomme segmentet. Hva er riktig?   A: Ja: høyest prosent av omsetningen betyr mest lønnsomt   B: Nei: prosenten er av omsetningen. Når timen er knapp, gir huseierne 293 kr i dekningsbidrag per time mot næringsbyggenes 916   C: Nei: huseierne betaler for sent til å være lønnsomme   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Anbefal Kari to målgrupper og en målgruppestrategi. Test valget mot de fire kravene i boka, og si hva Nordlys gjør med de andre segmentene. Bruk minst ett tall. Tre–fire setninger.</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">Timepris</t>
   </si>
   <si>
-    <t xml:space="preserve">890 kr uten mva</t>
+    <t xml:space="preserve">890 kr uten merverdiavgift</t>
   </si>
   <si>
     <t xml:space="preserve">Salgsinntekt første år</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">Haugerud-prosjektet</t>
   </si>
   <si>
-    <t xml:space="preserve">24 rekkehus, 1 800 timer på 6 mnd</t>
+    <t xml:space="preserve">24 rekkehus, 1 800 timer på 6 måneder</t>
   </si>
   <si>
     <t xml:space="preserve">Betaling</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">Boka bruker «differensiert» om ulike tilbud til ulike grupper (5.8.2) og «konsentrert» om å satse på ett eller noen få segmenter (5.8.3).</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 5.7 (fire krav, kapasitet) og 5.8 (målgruppestrategier); kap. 3.7.2 (Porter). Haugerud-prosjektet er fra MA02; konkurser i bygg: BDO gjengitt i Elektro24-7. Fjell Elektro AS og Haugerud Bygg AS er konstruerte casebedrifter; boligtallene for Oslo øst er konstruerte.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 5.7 (fire krav, kapasitet) og 5.8 (målgruppestrategier); kap. 3.7.2 (Porter). Haugerud-prosjektet er fra Markedsføring kap. 2; konkurser i bygg: BDO gjengitt i Elektro24-7. Fjell Elektro AS og Haugerud Bygg AS er konstruerte casebedrifter; boligtallene for Oslo øst er konstruerte.</t>
   </si>
 </sst>
 </file>
@@ -2036,7 +2036,7 @@
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
         <v>24</v>
       </c>

--- a/pensum/ma05/MA05_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma05/MA05_Klasseoppgaver_v5.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="154">
   <si>
-    <t xml:space="preserve">Klasseoppgaver til Markedsføring kapittel 5: Markedssegmentering (V5)</t>
+    <t xml:space="preserve">Klasseoppgaver til Markedsføring kapittel 5: Markedssegmentering (versjon 5)</t>
   </si>
   <si>
     <t xml:space="preserve">LØM · Fagskolen Oslo, Avdeling Elkraft · versjon 5, oktober 2026</t>

--- a/pensum/ma05/MA05_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma05/MA05_Klasseoppgaver_v5.xlsx
@@ -266,7 +266,7 @@
     <t xml:space="preserve">Kapasitet</t>
   </si>
   <si>
-    <t xml:space="preserve">3 500 fakturerbare timer i året</t>
+    <t xml:space="preserve">3 500 fakturerbare timer i året (2 × 1 400 + 700)</t>
   </si>
   <si>
     <t xml:space="preserve">Monas idé</t>
